--- a/model_comb3/EvalOutputs/TestDataset1_predictions_yolo.xlsx
+++ b/model_comb3/EvalOutputs/TestDataset1_predictions_yolo.xlsx
@@ -478,25 +478,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.500115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.499986</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.007709</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.005263</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2595</v>
+        <v>0.0002</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -512,25 +512,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.495113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.497441</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.017011</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.002788</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.3935</v>
       </c>
       <c r="I3" t="n">
-        <v>0.161</v>
+        <v>0.0003</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -549,22 +549,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.498581</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.503362</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.019281</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.002425</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9764</v>
+        <v>0.0221</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0305</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.496684</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>0.5005500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.011178</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.003109</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001</v>
+        <v>0.136</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0772</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -614,25 +614,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.827678</v>
+        <v>0.497808</v>
       </c>
       <c r="E6" t="n">
-        <v>0.571414</v>
+        <v>0.503543</v>
       </c>
       <c r="F6" t="n">
-        <v>0.168789</v>
+        <v>0.024386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.265968</v>
+        <v>0.006391</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.148579</v>
+        <v>0.49347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.201224</v>
+        <v>0.5062</v>
       </c>
       <c r="F7" t="n">
-        <v>0.241326</v>
+        <v>0.010346</v>
       </c>
       <c r="G7" t="n">
-        <v>0.166648</v>
+        <v>0.001548</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001</v>
@@ -682,25 +682,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.495733</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>0.509848</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.01296</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.000258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9999</v>
+        <v>0.999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0105</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.496795</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>0.50432</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.0223</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.001326</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.1512</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1451</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -750,25 +750,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.499042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.505976</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.026467</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.003923</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -784,25 +784,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.498729</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.505454</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.020006</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.003892</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.498917</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.5043570000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.008203</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.002707</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1148</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.1915</v>
       </c>
     </row>
     <row r="13">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.50099</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.5010869999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.017988</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.001863</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -886,25 +886,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.499201</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.50022</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.016343</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.001917</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.3619</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -920,25 +920,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.496379</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.501669</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.027496</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.001614</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0036</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -954,25 +954,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.496501</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.502631</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.019058</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.000434</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0052</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -991,25 +991,25 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.498581</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.503362</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.019281</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.002425</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9764</v>
+        <v>0.0221</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1402</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1022,28 +1022,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.865359</v>
+        <v>0.494785</v>
       </c>
       <c r="E18" t="n">
-        <v>0.459954</v>
+        <v>0.500465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124785</v>
+        <v>0.020638</v>
       </c>
       <c r="G18" t="n">
-        <v>0.171972</v>
+        <v>0.005563</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8929</v>
+        <v>0.8263</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="19">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.496684</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.5005500000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.011178</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.003109</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0001</v>
+        <v>0.136</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0756</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="20">
@@ -1090,25 +1090,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.498405</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>0.50075</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.012762</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.003621</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0001</v>
+        <v>0.0215</v>
       </c>
       <c r="I20" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.503504</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>0.50202</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.029225</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0.008031</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0058</v>
+        <v>0.0025</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1161,25 +1161,25 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>0.492565</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>0.505192</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.020543</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.002357</v>
       </c>
       <c r="H22" t="n">
-        <v>0.368</v>
+        <v>0.9999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1802</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1712</v>
       </c>
     </row>
     <row r="23">
@@ -1195,25 +1195,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.497308</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>0.502968</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.021915</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.006352</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9553</v>
+        <v>0.0905</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1817</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.3652</v>
       </c>
     </row>
     <row r="24">
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.497964</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>0.5012990000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.020226</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.006745</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5125</v>
+        <v>0.9992</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1681</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2603</v>
       </c>
     </row>
     <row r="25">
@@ -1263,25 +1263,25 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.495857</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>0.502124</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.019065</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.007058</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4017</v>
+        <v>0.9436</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1339</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.2444</v>
       </c>
     </row>
     <row r="26">
@@ -1294,25 +1294,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.499273</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>0.5003300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.011265</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.004188</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0092</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1328,25 +1328,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.500574</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>0.5021</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.016226</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.001907</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.499648</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5</v>
+        <v>0.504006</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0.010841</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.003627</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0106</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.497895</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.503553</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.007453</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.006052</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9993</v>
+        <v>0.9992</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0124</v>
+        <v>0.0003</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.4557</v>
       </c>
     </row>
     <row r="30">
@@ -1430,25 +1430,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.497207</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0.499059</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.004197</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.005881</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0352</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1464,28 +1464,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.498902</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.498663</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.014735</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0.0037</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9973</v>
+        <v>0.9918</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="32">
@@ -1498,28 +1498,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.500064</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5</v>
+        <v>0.503531</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.009131</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0.009313999999999999</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1301</v>
+        <v>0.0001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0022</v>
+        <v>0.1507</v>
       </c>
     </row>
     <row r="33">
@@ -1532,28 +1532,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.496123</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.509939</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.001317</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.007897</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0327</v>
+        <v>0.2761</v>
       </c>
     </row>
     <row r="34">
@@ -1566,28 +1566,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.48721</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>0.508139</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.008904</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.013642</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1276</v>
+        <v>0.001</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0934</v>
+        <v>0.7541</v>
       </c>
     </row>
     <row r="35">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0.492447</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5</v>
+        <v>0.50774</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.010035</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.009887</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2522</v>
+        <v>0.0004</v>
       </c>
       <c r="J35" t="n">
-        <v>0.044</v>
+        <v>0.6079</v>
       </c>
     </row>
     <row r="36">
@@ -1634,28 +1634,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.486174</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5</v>
+        <v>0.504609</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.012638</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0.001065</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0711</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.5696</v>
       </c>
     </row>
     <row r="37">
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.584317</v>
+        <v>0.493586</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60063</v>
+        <v>0.502302</v>
       </c>
       <c r="F37" t="n">
-        <v>0.400734</v>
+        <v>0.0235</v>
       </c>
       <c r="G37" t="n">
-        <v>0.40104</v>
+        <v>0.000636</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8559</v>
+        <v>0.9999</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0502</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0025</v>
+        <v>0.3351</v>
       </c>
     </row>
     <row r="38">
@@ -1702,28 +1702,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.50082</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>0.506349</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.003102</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0.006973</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0327</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.4063</v>
       </c>
     </row>
     <row r="39">
@@ -1736,28 +1736,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.499111</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.502544</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.006661</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.006641</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="I39" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.2628</v>
       </c>
     </row>
     <row r="40">
@@ -1770,28 +1770,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.493521</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>0.502877</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0.015891</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.001914</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0118</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2659</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5</v>
+        <v>0.498131</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5</v>
+        <v>0.499436</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0.013112</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.005021</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5724</v>
+        <v>0.7862</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0973</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -1841,25 +1841,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5</v>
+        <v>0.496981</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5</v>
+        <v>0.503073</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0.015325</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0157</v>
+        <v>0.9978</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1197</v>
+        <v>0.0001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0015</v>
+        <v>0.2793</v>
       </c>
     </row>
     <row r="43">
@@ -1872,28 +1872,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5</v>
+        <v>0.496381</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5</v>
+        <v>0.501598</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.015216</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2.6e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9906</v>
+        <v>0.9991</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2101</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
     </row>
     <row r="44">
@@ -1909,25 +1909,25 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5</v>
+        <v>0.498561</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5</v>
+        <v>0.5045500000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.022995</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0.003384</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6498</v>
+        <v>0.0001</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1373</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="45">
@@ -1940,25 +1940,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5</v>
+        <v>0.499453</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>0.5076040000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0.032092</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0.000344</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0891</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>

--- a/model_comb3/EvalOutputs/TestDataset1_predictions_yolo.xlsx
+++ b/model_comb3/EvalOutputs/TestDataset1_predictions_yolo.xlsx
@@ -481,22 +481,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.500115</v>
+        <v>0.345607</v>
       </c>
       <c r="E2" t="n">
-        <v>0.499986</v>
+        <v>0.557136</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007709</v>
+        <v>0.261926</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005263</v>
+        <v>0.280492</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -515,22 +515,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.495113</v>
+        <v>0.554458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.497441</v>
+        <v>0.482983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.017011</v>
+        <v>0.344421</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002788</v>
+        <v>0.476757</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3935</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003</v>
+        <v>0.5346</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -549,22 +549,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.498581</v>
+        <v>0.457605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.503362</v>
+        <v>0.294537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.019281</v>
+        <v>0.454618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002425</v>
+        <v>0.325046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0221</v>
+        <v>0.0005</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.1463</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -583,19 +583,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.496684</v>
+        <v>0.439247</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5005500000000001</v>
+        <v>0.269105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.011178</v>
+        <v>0.350824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003109</v>
+        <v>0.33164</v>
       </c>
       <c r="H5" t="n">
-        <v>0.136</v>
+        <v>0.2699</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -617,22 +617,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.497808</v>
+        <v>0.679171</v>
       </c>
       <c r="E6" t="n">
-        <v>0.503543</v>
+        <v>0.263906</v>
       </c>
       <c r="F6" t="n">
-        <v>0.024386</v>
+        <v>0.555895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006391</v>
+        <v>0.426148</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2017</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.49347</v>
+        <v>0.656169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5062</v>
+        <v>0.298442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.010346</v>
+        <v>0.563241</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001548</v>
+        <v>0.466054</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.0233</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -685,25 +685,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.495733</v>
+        <v>0.679215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.509848</v>
+        <v>0.581178</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01296</v>
+        <v>0.428476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000258</v>
+        <v>0.463491</v>
       </c>
       <c r="H8" t="n">
-        <v>0.999</v>
+        <v>0.9949</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1027</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1602</v>
       </c>
     </row>
     <row r="9">
@@ -719,19 +719,19 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.496795</v>
+        <v>0.7300219999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.50432</v>
+        <v>0.79771</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0223</v>
+        <v>0.328796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001326</v>
+        <v>0.350595</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1512</v>
+        <v>0.1973</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -753,19 +753,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.499042</v>
+        <v>0.729024</v>
       </c>
       <c r="E10" t="n">
-        <v>0.505976</v>
+        <v>0.6218669999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.026467</v>
+        <v>0.35676</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003923</v>
+        <v>0.420706</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -787,25 +787,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.498729</v>
+        <v>0.697762</v>
       </c>
       <c r="E11" t="n">
-        <v>0.505454</v>
+        <v>0.363345</v>
       </c>
       <c r="F11" t="n">
-        <v>0.020006</v>
+        <v>0.507978</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003892</v>
+        <v>0.383109</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.2391</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="12">
@@ -821,25 +821,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.498917</v>
+        <v>0.637973</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5043570000000001</v>
+        <v>0.343883</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008203</v>
+        <v>0.462668</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002707</v>
+        <v>0.359132</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0009</v>
+        <v>0.0018</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.4198</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1915</v>
+        <v>0.3576</v>
       </c>
     </row>
     <row r="13">
@@ -855,16 +855,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.50099</v>
+        <v>0.39907</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5010869999999999</v>
+        <v>0.449644</v>
       </c>
       <c r="F13" t="n">
-        <v>0.017988</v>
+        <v>0.413248</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001863</v>
+        <v>0.441376</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -889,22 +889,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.499201</v>
+        <v>0.453441</v>
       </c>
       <c r="E14" t="n">
-        <v>0.50022</v>
+        <v>0.582464</v>
       </c>
       <c r="F14" t="n">
-        <v>0.016343</v>
+        <v>0.151957</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001917</v>
+        <v>0.273715</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3619</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.0571</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.496379</v>
+        <v>0.766379</v>
       </c>
       <c r="E15" t="n">
-        <v>0.501669</v>
+        <v>0.511772</v>
       </c>
       <c r="F15" t="n">
-        <v>0.027496</v>
+        <v>0.251976</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001614</v>
+        <v>0.371579</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -957,16 +957,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.496501</v>
+        <v>0.620065</v>
       </c>
       <c r="E16" t="n">
-        <v>0.502631</v>
+        <v>0.501588</v>
       </c>
       <c r="F16" t="n">
-        <v>0.019058</v>
+        <v>0.281507</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000434</v>
+        <v>0.501359</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -991,25 +991,25 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.498581</v>
+        <v>0.457605</v>
       </c>
       <c r="E17" t="n">
-        <v>0.503362</v>
+        <v>0.294537</v>
       </c>
       <c r="F17" t="n">
-        <v>0.019281</v>
+        <v>0.454618</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002425</v>
+        <v>0.325046</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0221</v>
+        <v>0.0005</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.3361</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="18">
@@ -1022,28 +1022,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.494785</v>
+        <v>0.373899</v>
       </c>
       <c r="E18" t="n">
-        <v>0.500465</v>
+        <v>0.268831</v>
       </c>
       <c r="F18" t="n">
-        <v>0.020638</v>
+        <v>0.375758</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005563</v>
+        <v>0.34831</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8263</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.4242</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0384</v>
+        <v>0.0347</v>
       </c>
     </row>
     <row r="19">
@@ -1059,25 +1059,25 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.496684</v>
+        <v>0.439247</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5005500000000001</v>
+        <v>0.269105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.011178</v>
+        <v>0.350824</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003109</v>
+        <v>0.33164</v>
       </c>
       <c r="H19" t="n">
-        <v>0.136</v>
+        <v>0.2699</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.2457</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1093,22 +1093,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.498405</v>
+        <v>0.559425</v>
       </c>
       <c r="E20" t="n">
-        <v>0.50075</v>
+        <v>0.297308</v>
       </c>
       <c r="F20" t="n">
-        <v>0.012762</v>
+        <v>0.486342</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003621</v>
+        <v>0.366762</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0215</v>
+        <v>0.0021</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1127,22 +1127,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.503504</v>
+        <v>0.185455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.50202</v>
+        <v>0.532469</v>
       </c>
       <c r="F21" t="n">
-        <v>0.029225</v>
+        <v>0.279749</v>
       </c>
       <c r="G21" t="n">
-        <v>0.008031</v>
+        <v>0.281925</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0025</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1158,28 +1158,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.492565</v>
+        <v>0.451066</v>
       </c>
       <c r="E22" t="n">
-        <v>0.505192</v>
+        <v>0.28603</v>
       </c>
       <c r="F22" t="n">
-        <v>0.020543</v>
+        <v>0.263036</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002357</v>
+        <v>0.329234</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9999</v>
+        <v>0.4041</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1712</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="23">
@@ -1195,25 +1195,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.497308</v>
+        <v>0.477086</v>
       </c>
       <c r="E23" t="n">
-        <v>0.502968</v>
+        <v>0.290188</v>
       </c>
       <c r="F23" t="n">
-        <v>0.021915</v>
+        <v>0.430653</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006352</v>
+        <v>0.374249</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0905</v>
+        <v>0.0451</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.5375</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3652</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="24">
@@ -1229,25 +1229,25 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.497964</v>
+        <v>0.454533</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5012990000000001</v>
+        <v>0.252106</v>
       </c>
       <c r="F24" t="n">
-        <v>0.020226</v>
+        <v>0.374229</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006745</v>
+        <v>0.344598</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9992</v>
+        <v>0.6014</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.4734</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2603</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="25">
@@ -1260,28 +1260,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.495857</v>
+        <v>0.493786</v>
       </c>
       <c r="E25" t="n">
-        <v>0.502124</v>
+        <v>0.264377</v>
       </c>
       <c r="F25" t="n">
-        <v>0.019065</v>
+        <v>0.352877</v>
       </c>
       <c r="G25" t="n">
-        <v>0.007058</v>
+        <v>0.325674</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9436</v>
+        <v>0.0445</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.2456</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2444</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="26">
@@ -1297,19 +1297,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.499273</v>
+        <v>0.678655</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5003300000000001</v>
+        <v>0.342095</v>
       </c>
       <c r="F26" t="n">
-        <v>0.011265</v>
+        <v>0.492334</v>
       </c>
       <c r="G26" t="n">
-        <v>0.004188</v>
+        <v>0.420348</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1331,19 +1331,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.500574</v>
+        <v>0.693867</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5021</v>
+        <v>0.297372</v>
       </c>
       <c r="F27" t="n">
-        <v>0.016226</v>
+        <v>0.536772</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001907</v>
+        <v>0.466225</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.499648</v>
+        <v>0.332762</v>
       </c>
       <c r="E28" t="n">
-        <v>0.504006</v>
+        <v>0.575823</v>
       </c>
       <c r="F28" t="n">
-        <v>0.010841</v>
+        <v>0.309217</v>
       </c>
       <c r="G28" t="n">
-        <v>0.003627</v>
+        <v>0.42867</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9737</v>
+        <v>0.3593</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.497895</v>
+        <v>0.496956</v>
       </c>
       <c r="E29" t="n">
-        <v>0.503553</v>
+        <v>0.497916</v>
       </c>
       <c r="F29" t="n">
-        <v>0.007453</v>
+        <v>0.32804</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006052</v>
+        <v>0.48681</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9992</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0003</v>
+        <v>0.528</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1433,22 +1433,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.497207</v>
+        <v>0.432342</v>
       </c>
       <c r="E30" t="n">
-        <v>0.499059</v>
+        <v>0.438631</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004197</v>
+        <v>0.418303</v>
       </c>
       <c r="G30" t="n">
-        <v>0.005881</v>
+        <v>0.448187</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9999</v>
+        <v>0.9986</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.0473</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1467,25 +1467,25 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.498902</v>
+        <v>0.185808</v>
       </c>
       <c r="E31" t="n">
-        <v>0.498663</v>
+        <v>0.42953</v>
       </c>
       <c r="F31" t="n">
-        <v>0.014735</v>
+        <v>0.314869</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0037</v>
+        <v>0.374717</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9918</v>
+        <v>0.9953</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.1193</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2218</v>
+        <v>0.1572</v>
       </c>
     </row>
     <row r="32">
@@ -1501,25 +1501,25 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.500064</v>
+        <v>0.627066</v>
       </c>
       <c r="E32" t="n">
-        <v>0.503531</v>
+        <v>0.504004</v>
       </c>
       <c r="F32" t="n">
-        <v>0.009131</v>
+        <v>0.486317</v>
       </c>
       <c r="G32" t="n">
-        <v>0.009313999999999999</v>
+        <v>0.5209589999999999</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0001</v>
+        <v>0.3782</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1507</v>
+        <v>0.1412</v>
       </c>
     </row>
     <row r="33">
@@ -1535,25 +1535,25 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.496123</v>
+        <v>0.514392</v>
       </c>
       <c r="E33" t="n">
-        <v>0.509939</v>
+        <v>0.547693</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001317</v>
+        <v>0.525451</v>
       </c>
       <c r="G33" t="n">
-        <v>0.007897</v>
+        <v>0.513385</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.3489</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2761</v>
+        <v>0.2689</v>
       </c>
     </row>
     <row r="34">
@@ -1569,25 +1569,25 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.48721</v>
+        <v>0.538866</v>
       </c>
       <c r="E34" t="n">
-        <v>0.508139</v>
+        <v>0.490865</v>
       </c>
       <c r="F34" t="n">
-        <v>0.008904</v>
+        <v>0.419168</v>
       </c>
       <c r="G34" t="n">
-        <v>0.013642</v>
+        <v>0.320249</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.001</v>
+        <v>0.4467</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7541</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="35">
@@ -1603,25 +1603,25 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.492447</v>
+        <v>0.546699</v>
       </c>
       <c r="E35" t="n">
-        <v>0.50774</v>
+        <v>0.511888</v>
       </c>
       <c r="F35" t="n">
-        <v>0.010035</v>
+        <v>0.628149</v>
       </c>
       <c r="G35" t="n">
-        <v>0.009887</v>
+        <v>0.577524</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0004</v>
+        <v>0.371</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6079</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="36">
@@ -1637,25 +1637,25 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.486174</v>
+        <v>0.743003</v>
       </c>
       <c r="E36" t="n">
-        <v>0.504609</v>
+        <v>0.553349</v>
       </c>
       <c r="F36" t="n">
-        <v>0.012638</v>
+        <v>0.386318</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001065</v>
+        <v>0.513218</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.5294</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5696</v>
+        <v>0.1961</v>
       </c>
     </row>
     <row r="37">
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.493586</v>
+        <v>0.672851</v>
       </c>
       <c r="E37" t="n">
-        <v>0.502302</v>
+        <v>0.523643</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0235</v>
+        <v>0.332202</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000636</v>
+        <v>0.265596</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9999</v>
+        <v>0.024</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1705,25 +1705,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.50082</v>
+        <v>0.776468</v>
       </c>
       <c r="E38" t="n">
-        <v>0.506349</v>
+        <v>0.516162</v>
       </c>
       <c r="F38" t="n">
-        <v>0.003102</v>
+        <v>0.333384</v>
       </c>
       <c r="G38" t="n">
-        <v>0.006973</v>
+        <v>0.38369</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.4582</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4063</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="39">
@@ -1739,25 +1739,25 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.499111</v>
+        <v>0.716965</v>
       </c>
       <c r="E39" t="n">
-        <v>0.502544</v>
+        <v>0.492815</v>
       </c>
       <c r="F39" t="n">
-        <v>0.006661</v>
+        <v>0.306542</v>
       </c>
       <c r="G39" t="n">
-        <v>0.006641</v>
+        <v>0.279936</v>
       </c>
       <c r="H39" t="n">
-        <v>0.997</v>
+        <v>0.9951</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0002</v>
+        <v>0.3584</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2628</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="40">
@@ -1773,22 +1773,22 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.493521</v>
+        <v>0.630071</v>
       </c>
       <c r="E40" t="n">
-        <v>0.502877</v>
+        <v>0.384802</v>
       </c>
       <c r="F40" t="n">
-        <v>0.015891</v>
+        <v>0.534856</v>
       </c>
       <c r="G40" t="n">
-        <v>0.001914</v>
+        <v>0.482449</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07829999999999999</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.1037</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1804,25 +1804,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.498131</v>
+        <v>0.390804</v>
       </c>
       <c r="E41" t="n">
-        <v>0.499436</v>
+        <v>0.415046</v>
       </c>
       <c r="F41" t="n">
-        <v>0.013112</v>
+        <v>0.503144</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005021</v>
+        <v>0.458159</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7862</v>
+        <v>0.0673</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.4263</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -1841,25 +1841,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.496981</v>
+        <v>0.448491</v>
       </c>
       <c r="E42" t="n">
-        <v>0.503073</v>
+        <v>0.577338</v>
       </c>
       <c r="F42" t="n">
-        <v>0.015325</v>
+        <v>0.276673</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0007</v>
+        <v>0.383692</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9978</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0001</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2793</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="43">
@@ -1872,28 +1872,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.496381</v>
+        <v>0.461615</v>
       </c>
       <c r="E43" t="n">
-        <v>0.501598</v>
+        <v>0.741739</v>
       </c>
       <c r="F43" t="n">
-        <v>0.015216</v>
+        <v>0.453721</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6e-05</v>
+        <v>0.419749</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9991</v>
+        <v>0.0334</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.5746</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5019</v>
+        <v>0.1737</v>
       </c>
     </row>
     <row r="44">
@@ -1909,25 +1909,25 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.498561</v>
+        <v>0.32902</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5045500000000001</v>
+        <v>0.597139</v>
       </c>
       <c r="F44" t="n">
-        <v>0.022995</v>
+        <v>0.228845</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003384</v>
+        <v>0.452219</v>
       </c>
       <c r="H44" t="n">
         <v>0.0001</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.4006</v>
       </c>
       <c r="J44" t="n">
-        <v>0.148</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1943,22 +1943,22 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.499453</v>
+        <v>0.496852</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5076040000000001</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.032092</v>
+        <v>0.660485</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000344</v>
+        <v>0.674912</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
